--- a/Rstudio/Dynamic chambers/Cattle Final NH3.xlsx
+++ b/Rstudio/Dynamic chambers/Cattle Final NH3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzobenedetti/Documents/GitHub/Benedetti-2026-N2O-AgroscenaNext/Rstudio/Dynamic chambers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFCEC558-2A15-8C43-964C-43E48E52F323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79EC9798-3232-5B4F-8AE1-296739AF3DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16600" xr2:uid="{1C17C28D-1FA2-AE49-AC6E-A2CF747B5228}"/>
+    <workbookView xWindow="35480" yWindow="2420" windowWidth="27640" windowHeight="16600" xr2:uid="{1C17C28D-1FA2-AE49-AC6E-A2CF747B5228}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="8">
   <si>
     <t>VALVE_ID</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>N-NH3 perc TAN</t>
+  </si>
+  <si>
+    <t>BLOCK</t>
   </si>
 </sst>
 </file>
@@ -458,150 +461,180 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{467644BA-9052-2C47-B92D-96324B4A9557}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3">
+      <c r="D2" s="3">
         <v>3.2982504650736675</v>
       </c>
-      <c r="D2" s="3">
+      <c r="E2" s="3">
         <v>10.400429257149124</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3">
+      <c r="D3" s="3">
         <v>3.7080232773527686</v>
       </c>
-      <c r="D3" s="3">
+      <c r="E3" s="3">
         <v>11.6798191811445</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>17</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4">
         <v>3</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
         <v>2.4937305125855955</v>
       </c>
-      <c r="D4" s="3">
+      <c r="E4" s="3">
         <v>7.8538311758294217</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3">
+      <c r="D5" s="3">
         <v>2.3159966433127703</v>
       </c>
-      <c r="D5" s="3">
+      <c r="E5" s="3">
         <v>7.2087937332059644</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="3">
+      <c r="D6" s="3">
         <v>3.7250602908692567</v>
       </c>
-      <c r="D6" s="3">
+      <c r="E6" s="3">
         <v>11.58758250261207</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>18</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="3">
+      <c r="D7" s="3">
         <v>3.5623815803567083</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E7" s="3">
         <v>11.075102587534355</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>11</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="3">
+      <c r="D8" s="3">
         <v>5.0944412908455599</v>
       </c>
-      <c r="D8" s="3">
+      <c r="E8" s="3">
         <v>14.715248426159382</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>13</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4">
+        <v>2</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="3">
+      <c r="D9" s="3">
         <v>5.6960246412389379</v>
       </c>
-      <c r="D9" s="3">
+      <c r="E9" s="3">
         <v>16.396869698333497</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>15</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4">
+        <v>3</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="3">
+      <c r="D10" s="3">
         <v>5.3870083815118628</v>
       </c>
-      <c r="D10" s="3">
+      <c r="E10" s="3">
         <v>15.545333774188622</v>
       </c>
     </row>
